--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.123" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.123" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.123.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0123.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0123.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.123" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.123" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: å¤š</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+591A CJK UNIFIED IDEOGRAPH-591A | isolated marker/symbol line :: 多</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ to</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]116 MISCELLANEOUS ORDERS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]116 MISCELLANEOUS ORDERS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 116</t>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -684,19 +688,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: å¤š</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+591A CJK UNIFIED IDEOGRAPH-591A | isolated marker/symbol line :: 多</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L12: isolated marker/symbol line :: a</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+591A CJK UNIFIED IDEOGRAPH-591A | isolated marker/symbol line :: 多</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -709,7 +713,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L63: line starts with digit/letter garbage token | suspicious token(s): 9Payment (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Order 36 Payment" vs "9Payment" :: 9Payment by proceed by reason of the Solicitor for any party having</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -742,23 +746,31 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 2</t>
+          <t>L12: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L63: line starts with digit/letter garbage token | suspicious token(s): 9Payment (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Order 36 Payment" vs "9Payment" :: 9Payment by proceed by reason of the Solicitor for any party having</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -779,7 +791,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -794,7 +806,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 5</t>
+          <t>L33: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -837,7 +849,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 116</t>
+          <t>L70: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -880,7 +892,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: a</t>
+          <t>L71: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -923,7 +935,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 2</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+591A CJK UNIFIED IDEOGRAPH-591A | isolated marker/symbol line :: 多</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -966,7 +978,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 5</t>
+          <t>L86: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -994,7 +1006,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1007,7 +1019,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L107: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1033,7 +1049,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1046,7 +1062,11 @@
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L144: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1067,7 +1087,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1150,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
